--- a/docs/sales/営業リスト.xlsx
+++ b/docs/sales/営業リスト.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リスト" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="紹介元" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="知人20人" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="訪問記録" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="週次の数" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="調べた範囲" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リスト" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="紹介元" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="知人20人" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="訪問記録" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="週次の数" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'リスト'!$A$1:$P$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'リスト'!$A$1:$P$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -637,6 +638,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>調べた範囲と限界（2026-10-25 時点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>・見たもの：ハローワーク求人の転載ページ（hellowork.careers）の上山市（食品製造・建設・旅館）と山形市（建設）、求人ジャーナル／シゴトサガスの上山市一覧。会社概要は求人サイトの記載のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>・載せたのは、求人を出している事実（職種・受理日）だけ。受理日の年は表示がないため、掲載日の流れから2026年と読んでいる</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>・「規模」「外国人雇用の気配」は、見たページに記載がなく、すべて「不明」。外国人・技能実習の記載は1件も見つからなかった。→ 監理団体・登録支援機関・商工会経由で探す</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>・「求人継続」は、一時点の掲載では判定できないため「不明」。次の確認（1月ごろ）で同じ会社がまだ出していれば「3か月以上」に直す。それまで確認日を残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>・優先度はすべて仮のB（入口＝誰経由かが決まっていないため）。入口が見えた会社をAにする</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>・入れていない会社：派遣・人材会社（綜合キャリアオプション、マイセルフ等）、東和薬品 山形工場（大企業）、運送・警備・小売大手。ソエギの相手（5〜50人）と合わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>・旅館は、山形市の見本・上山市の旅館の求人が多数ある。ただし多言語の需要は求人からは分からない（旅館の求人に外国語の要件は見つからなかった）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>・まだ見ていない：2ページ目以降の求人、会社の公式サイト、山形県の建設業許可業者名簿、ほかの市町村（天童・山形市の食品・繊維など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>・商工会の会員名簿は使っていない（紹介してもらうときだけ）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -744,381 +832,1331 @@
       <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>丸松物産株式会社 山形工場</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>製造(食品)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M2" s="6" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-      <c r="P2" s="6" t="n"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>食品製造ラインの正社員・パートを3本（受理8/3・8/24・8/25、〜10/31）＋製造ライン管理・生産管理（10/19掲載）。メンマなど業務用の農産調理品の工場（求人サイトの記載）</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E9%A3%9F%E5%93%81%E8%A3%BD%E9%80%A0%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>株式会社蔵王ミート</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>製造(食品)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M3" s="6" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="5" t="n"/>
-      <c r="P3" s="6" t="n"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>食肉処理・加工の正社員（求番06010-14932861、受理8/20、〜10/31）</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E9%A3%9F%E5%93%81%E8%A3%BD%E9%80%A0%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>株式会社鮒忠 山形営業所</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>卸・小売</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M4" s="6" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-      <c r="P4" s="6" t="n"/>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>卸売営業（配送含む）の正社員（求番13030-12369761、受理8/4、〜10/31）</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E9%A3%9F%E5%93%81%E8%A3%BD%E9%80%A0%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>堀川土建株式会社</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="6" t="n"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>上山市矢来。現場作業員（10/15）・建築施工管理（10/1）をHW掲載、除雪スタッフ（〜11/13・求人ジャーナル）、doda経由の建築施工管理（7/16掲載）。公共工事ほぼ100%、従業員は「11〜100人」の区分（マイナビエージェント）</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>株式会社 鳶 五十嵐組</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M6" s="6" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="6" t="n"/>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>鳶・クレーン・土木の正社員（求番06010-18487861、受理10/7）</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>有限会社 大和建設</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="6" t="n"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>施工管理（現場監督・10/2）と見習い（8/27）の2本。施工管理は月給28〜48万円</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>西庄建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="6" t="n"/>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>現場作業員の正社員（求番06010-17479061、受理10/1）</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>株式会社 旅館古窯</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>宿・旅館</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M9" s="6" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="6" t="n"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>正社員（調理・接客・設備点検）とパートを複数、9/1〜10/19に繰り返し掲載（HW）</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E6%97%85%E9%A4%A8%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>株式会社 月岡ホテル</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>宿・旅館</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="6" t="n"/>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>経理事務（10/1）・調理補助（10/1）・予約受付（8/17）をHW掲載。調理スタッフ（寮あり）は7/16掲載（広告）</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E6%97%85%E9%A4%A8%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>株式会社 ホテル月の池</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>宿・旅館</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="6" t="n"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>ナイトフロント（9/25）・接客（9/14）・客室清掃（8/21）をHW掲載。広告に「花明りの宿 月の池」の調理求人（10/22）があるが同一かは未確認</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E6%97%85%E9%A4%A8%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>有限会社 有馬館</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>宿・旅館</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="6" t="n"/>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>清掃係（パート・9/2受理）。予約サイトの記載で客室35室（新湯）</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E6%97%85%E9%A4%A8%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>株式会社 彩花亭時代屋</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>宿・旅館</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="6" t="n"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>旅館の接客スタッフ（未経験歓迎・10/1受理）</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E6%97%85%E9%A4%A8%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>株式会社 葉山館</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>上山市</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>宿・旅館</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="6" t="n"/>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>調理部 食器準備係の正社員（9/1受理）</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E6%97%85%E9%A4%A8%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E4%B8%8A%E5%B1%B1%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>小白川建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>山形市</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="6" t="n"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>公共工事などの施工管理（月給35〜50万円・10/9受理）</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E5%B1%B1%E5%BD%A2%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>矢口建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>山形市</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="6" t="n"/>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>土木・建築・管工事の作業員と現場管理を2本（10/15受理）</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E5%B1%B1%E5%BD%A2%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>荻野建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>山形市</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="6" t="n"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>建築現場の管理（10/13受理）</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E5%B1%B1%E5%BD%A2%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>勝村建設 株式会社</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>山形市</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="6" t="n"/>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>公共工事の作業（60歳以上歓迎・10/22受理）</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E5%B1%B1%E5%BD%A2%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>株式会社 イシカワ</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>山形市</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="6" t="n"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>木造住宅の現場管理（10/22受理）</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E5%B1%B1%E5%BD%A2%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>株式会社 木川道路</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>山形市</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>（未定）</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
       <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="6" t="n"/>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>舗装工事・小規模土木・除雪（10/15受理）</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.careers/%E5%BB%BA%E8%A8%AD%E9%96%A2%E9%80%A3%E3%81%AE%E3%83%8F%E3%83%AD%E3%83%BC%E3%83%AF%E3%83%BC%E3%82%AF%E6%B1%82%E4%BA%BA%E5%B1%B1%E5%BD%A2%E7%9C%8C+%E5%B1%B1%E5%BD%A2%E5%B8%82</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>46320</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -4769,7 +5807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5861,7 +6899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6415,7 +7453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9134,7 +10172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/sales/営業リスト.xlsx
+++ b/docs/sales/営業リスト.xlsx
@@ -638,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -696,7 +696,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>・旅館は、山形市の見本・上山市の旅館の求人が多数ある。ただし多言語の需要は求人からは分からない（旅館の求人に外国語の要件は見つからなかった）</t>
+          <t>・旅館は、上山市で求人を出している宿が多い。ただし多言語の需要は求人からは分からない（外国語の要件を書いた求人は見つからなかった）</t>
         </is>
       </c>
     </row>
@@ -714,6 +714,10 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sales/営業リスト.xlsx
+++ b/docs/sales/営業リスト.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -114,6 +114,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -638,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -714,10 +717,27 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>・【追加調査 10/25】外国人を雇う会社は名簿が非公開で、公開情報から特定できなかった。代わりに、入口になる監理団体・登録支援機関・税理士を「紹介元」シートに出典つきで入れた</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>・紹介元の住所・電話・受入国・職種は、民間の紹介サイトの掲載（古い可能性あり）。連絡の前に、外国人技能実習機構・出入国在留管理庁の公開情報か、各団体のサイトで確かめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>・上山市商工会の公開連絡先は見つからなかった（10/26の訪問は、会う前に電話番号を確かめる）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -853,27 +873,27 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>51人以上</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>（未定）</t>
+          <t>（未定）：電話 023-673-5511（会社案内）</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -890,7 +910,7 @@
       <c r="M2" s="6" t="n"/>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>食品製造ラインの正社員・パートを3本（受理8/3・8/24・8/25、〜10/31）＋製造ライン管理・生産管理（10/19掲載）。メンマなど業務用の農産調理品の工場（求人サイトの記載）</t>
+          <t>食品製造ラインの正社員・パートを3本（受理8/3・8/24・8/25、〜10/31）＋製造ライン管理・生産管理（10/19掲載）。メンマなど業務用の農産調理品の工場（求人サイトの記載）。自社の会社案内（2022年4月時点）で山形工場の従業員は約100名・FSSC22000認証。ソエギの相手の規模（5〜50人）より大きい</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
@@ -5822,7 +5842,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -5830,7 +5850,7 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -5904,7 +5924,7 @@
           <t>上山市商工会</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr"/>
+      <c r="D2" s="5" t="n"/>
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>訪問（10/26 予定）</t>
@@ -5923,7 +5943,11 @@
         </is>
       </c>
       <c r="J2" s="6" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>連絡先は未確認（公開の電話・住所を探せなかった）。法人番号 4390005002511。経営発達支援計画の実施者</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -5939,7 +5963,7 @@
           <t>よろず支援拠点（山形）</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>進捗報告（11月中旬）</t>
@@ -5958,7 +5982,7 @@
         </is>
       </c>
       <c r="J3" s="6" t="n"/>
-      <c r="K3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -5966,19 +5990,23 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>税理士</t>
+          <t>登録支援機関</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>（3事務所：11月上旬にあいさつ）</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
+          <t>キャプラスクインターナショナル合同会社</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>建設・卸小売</t>
+          <t>外国人を雇う製造業</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -5989,7 +6017,11 @@
         </is>
       </c>
       <c r="J4" s="6" t="n"/>
-      <c r="K4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>上山市中生居545／050-5434-8065。上山市内の登録支援機関（特定技能の受入れ支援）。出典: amazing-human.jp（民間の掲載・古い可能性あり。出典: https://amazing-human.jp/yamagata-touroku/ ／ https://amazing-human.jp/intern-yamagata/）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -5997,19 +6029,23 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>社労士</t>
+          <t>監理団体</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>（社労士事務所）</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
+          <t>SISEI協同組合</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>製造・外国人雇用</t>
+          <t>製造・繊維・外国人を雇う製造業</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -6020,7 +6056,11 @@
         </is>
       </c>
       <c r="J5" s="6" t="n"/>
-      <c r="K5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>山形市大字漆山3423-1／023-664-2644。一般監理。受入国：中国・ベトナム・カンボジア・フィリピン。ニット製品製造も扱う（ジェイジャパン掲載）。登録支援機関としても掲載。出典: amazing-human.jp（民間の掲載・古い可能性あり。出典: https://amazing-human.jp/yamagata-touroku/ ／ https://amazing-human.jp/intern-yamagata/）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -6033,14 +6073,18 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>（2か所：11月中旬に相談）</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
+          <t>協同組合ソシアルジャパン山形</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>外国人を雇う製造業</t>
+          <t>建設・機械金属・農業</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -6051,7 +6095,11 @@
         </is>
       </c>
       <c r="J6" s="6" t="n"/>
-      <c r="K6" s="5" t="n"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>山形市香澄町。育成就労・特定技能の監理支援機関・登録支援機関として掲載。受入国：ベトナム。出典: gaikokusaiyo.com/agency/19959/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -6059,15 +6107,23 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>登録支援機関</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
+          <t>監理団体</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>PCJ協同組合</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>外国人を雇う製造業</t>
+          <t>（職種未確認）</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -6078,172 +6134,440 @@
         </is>
       </c>
       <c r="J7" s="6" t="n"/>
-      <c r="K7" s="5" t="n"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>山形市大手町5-4 レジデンス霞城202。特定監理事業として掲載。出典: ぐるっとAsia 掲載</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>監理団体</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>山形県中小企業振興事業協同組合／山形県中小企業振興協同組合</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>農業・建設・機械金属</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n"/>
-      <c r="K8" s="5" t="n"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>山辺町近江17-45。特定監理（中国）。同住所で2団体が掲載（関係は未確認）。出典: amazing-human.jp（民間の掲載・古い可能性あり。出典: https://amazing-human.jp/yamagata-touroku/ ／ https://amazing-human.jp/intern-yamagata/）</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>監理団体</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>協同組合ボンズ</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>（職種未確認）</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n"/>
-      <c r="K9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>東根市中央2-12-7。特定監理（ベトナム）。出典: amazing-human.jp（民間の掲載・古い可能性あり。出典: https://amazing-human.jp/yamagata-touroku/ ／ https://amazing-human.jp/intern-yamagata/）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>登録支援機関</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>株式会社DMC天童温泉</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>宿・旅館（推測）</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n"/>
-      <c r="K10" s="5" t="n"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>天童市鎌田1-3-38／023-654-6699。登録支援機関として掲載（宿との関係は未確認）。出典: amazing-human.jp/yamagata-touroku/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>登録支援機関</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>川越政伸行政書士事務所</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>外国人雇用の手続き</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J11" s="6" t="n"/>
-      <c r="K11" s="5" t="n"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>寒河江市大字島383-23／0237-86-7198。登録支援機関として掲載。行政書士＝補助金・在留手続きの紹介元にもなり得る</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>登録支援機関</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>一般社団法人全国人材支援連合会（山形県支部）</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>外国人雇用</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J12" s="6" t="n"/>
-      <c r="K12" s="5" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>山形市花楯2-18-70／090-6786-7920（住所欄の記載。本文には米沢市とあり不一致）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>監理団体（繊維）</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>山形縫製協同組合（酒田市）／山形アパレル工業協同組合（鶴岡市）／山形ファッションサポート協同組合（酒田市）</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>直接連絡</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>縫製・繊維</t>
+        </is>
+      </c>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J13" s="6" t="n"/>
-      <c r="K13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>庄内の組合。村山地域のニット（山辺町・寒河江市）の受入れは未確認。出典: amazing-human.jp（民間の掲載・古い可能性あり。出典: https://amazing-human.jp/yamagata-touroku/ ／ https://amazing-human.jp/intern-yamagata/）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>税理士</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>税理士法人おおぞら総合会計事務所 上山事務所</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>あいさつ（11月上旬）</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>建設・卸小売</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>上山市の税理士として税理士ドットコムに掲載（住所・電話は未確認）。出典: https://www.zeiri4.com/s_1121616/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>税理士</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>小野勝政税理士事務所</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>あいさつ（11月上旬）</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>建設・卸小売</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J15" s="6" t="n"/>
-      <c r="K15" s="5" t="n"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>上山市。税理士ドットコム掲載。出典: https://www.zeiri4.com/s_1121615/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>税理士</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>吉田俊雄税理士事務所</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>あいさつ（11月上旬）</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>建設・卸小売</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J16" s="6" t="n"/>
-      <c r="K16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>上山市。税理士ドットコム掲載。出典: https://www.zeiri4.com/s_1121615/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>税理士</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>安孫子和幸税理士事務所／ひなた税理士法人</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>あいさつ（11月上旬）</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>建設・卸小売</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="n"/>
-      <c r="K17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>上山市。ミツモア掲載。出典: https://meetsmore.com/t/tax-accountant/yamagata/kaminoyama</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>社労士</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>（上山市内の社労士は見つからず。県社労士会の会員検索で西村山・村山の事務所を探す）</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>あいさつ（11月上旬）</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>製造・外国人雇用</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>未連絡</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="n"/>
-      <c r="K18" s="5" t="n"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>要調査</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
